--- a/FIFA.xlsx
+++ b/FIFA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-Ana\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F094C9-7DFB-4FAA-9EA1-5F9A39F0C40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3C7E13-8D26-4CD0-8624-A2366102BDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" activeTab="1" xr2:uid="{BB1EA6DA-86EB-4FC3-997E-079B42B60F51}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" activeTab="2" xr2:uid="{BB1EA6DA-86EB-4FC3-997E-079B42B60F51}"/>
   </bookViews>
   <sheets>
     <sheet name="GROUP1" sheetId="2" r:id="rId1"/>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -493,6 +493,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1363,6 +1364,53 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{859B9908-9B66-4474-8DC9-5BE216207289}">
+  <we:reference id="wa200004935" version="6.1.0.0" store="en-GB" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200004935" version="6.1.0.0" store="WA200004935" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_FORMULABOT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_SENTIMENT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_INFO</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_FREEFORM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_INFER</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CFA40186-0FAC-41D1-A548-3C0D5B76493A}">
+  <we:reference id="wa200000113" version="1.0.0.0" store="en-GB" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200000113" version="1.0.0.0" store="WA200000113" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E23B7C48-8229-4FB4-8B7A-ED153A6D01FB}">
   <dimension ref="A1:G75"/>
@@ -3073,7 +3121,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DCCB2B-D478-46D6-A28C-AF9367C09B36}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="21.33203125" customWidth="1"/>
@@ -3101,6 +3149,231 @@
       <c r="G1" s="6" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
